--- a/outputs/content-system-prompts/content-system-outline-prompt-import-test.xlsx
+++ b/outputs/content-system-prompts/content-system-outline-prompt-import-test.xlsx
@@ -1,76 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt导入模板" sheetId="1" r:id="Rcbfc068ca1e04b00"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt导入模板" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0F172A"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="8">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -219,53 +286,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="33.33000183105469" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="75.55999755859375" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24.440000534057617" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="7.78000020980835" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>分类</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>标题</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
-        <x:v>简介</x:v>
-      </x:c>
-      <x:c r="D1" s="6" t="str">
-        <x:v>Prompt内容</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="str">
-        <x:v>标签</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="str">
-        <x:v>调用模式</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>启用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="195" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>自媒体</x:v>
-      </x:c>
-      <x:c r="B2" s="7" t="str">
-        <x:v>文章大纲</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="str">
-        <x:v>把选定题目整理成可确认、可写作的文章大纲。</x:v>
-      </x:c>
-      <x:c r="D2" s="7" t="str">
-        <x:v>请把以下选题整理成文章大纲 outline，不写正文。
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.4399995803833" customWidth="1" min="1" max="1"/>
+    <col width="28.88999938964844" customWidth="1" min="2" max="2"/>
+    <col width="33.33000183105469" customWidth="1" min="3" max="3"/>
+    <col width="75.55999755859375" customWidth="1" min="4" max="4"/>
+    <col width="24.44000053405762" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="7.78000020980835" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>简介</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Prompt内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="195" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>自媒体</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>文章大纲</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>把选定题目整理成可确认、可写作的文章大纲。</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>请把以下选题整理成文章大纲 outline，不写正文。
 选题来源：{{选题来源}}
 主要想说：{{核心判断}}
 目标读者：{{目标读者}}
@@ -279,19 +357,11 @@
 5. 必须输出独立的文章大纲，不能用推荐框架代替大纲。
 6. 大纲每节必须包含：章节标题、要回答的问题、关键内容、可使用素材。
 7. 软件介绍或教程类选题必须覆盖实际使用路径：安装/入口、初始化、核心操作、典型工作流、权限/边界、维护方法。
-8. 必须包含风险提醒，并最后展示核心判断、切入角度、文章大纲摘要，等待确认。</x:v>
-      </x:c>
-      <x:c r="E2" s="7" t="str">
-        <x:v>content-system,outline,文章大纲,SCQA</x:v>
-      </x:c>
-      <x:c r="F2" s="7" t="str">
-        <x:v>copy</x:v>
-      </x:c>
-      <x:c r="G2" s="7" t="str">
-        <x:v>true</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+8. 必须包含风险提醒，并最后展示核心判断、切入角度、文章大纲摘要，等待确认。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>